--- a/reaktory_variant2/Реакторы_вариант2_графики.xlsx
+++ b/reaktory_variant2/Реакторы_вариант2_графики.xlsx
@@ -470,7 +470,8 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -707,7 +708,8 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -724,7 +726,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3600000"/>
+    <ext cx="6480000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -746,7 +748,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3600000"/>
+    <ext cx="6480000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>

--- a/reaktory_variant2/Реакторы_вариант2_графики.xlsx
+++ b/reaktory_variant2/Реакторы_вариант2_графики.xlsx
@@ -3582,7 +3582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3803,18 +3803,18 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Выводы</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
+          <t>Вывод</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="220" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>1. Для всех трёх кинетических случаев РИВ даёт большую степень превращения X и большую производительность ΠR по целевому продукту R, чем РИС-н того же объёма (τ = 2 мин). Это ожидаемо: в РИС-н вся реакция идёт при низкой выходной CA, скорость A→R меньше.
-2. Селективность. В случаях 1 и 2 (n2 = 1) дифференциальная S на выходе РИС-н одинакова (0,5556), потому что отношение скоростей на выходе определяется k1, k2 и порядками. Интегральная SR = Y/X совпадает с S для РИС-н (идеальное смешение). В РИВ SR выше, чем в РИС-н: случай 1 — 0,620 против 0,556; случай 2 — 0,636 против 0,556; случай 3 — 0,808 против 0,753.
-3. Случай 3 (n2 = 2) наиболее выгоден по целевому продукту: побочная R→S второго порядка, CS растёт медленнее, Y и ΠR максимальны (РИВ: CR = 16,95 моль/л, ΠR = 50,84 кмоль/ч).
-4. Случай 1 (n1 = 2) наименее выгоден: вторая реакция по A тормозит превращение, X и ΠR минимальны.
-5. Для графиков выбран случай 1 (как на скриншотах РИВ с полной сеткой τ). Точки на графике — квадраты (CA), звёзды (CR) и кресты-звёздочки (CS), линии сглаженные, как в Kniga1.xlsx.</t>
+          <t>Моделирование последовательной реакции A → R → S выполнено в изотермическом режиме (T = 150 °C) для реакторов идеального смешения непрерывного действия (РИС-н) и идеального вытеснения (РИВ) одинакового объёма: V = 100 л, v0 = 50 л/мин, условное время пребывания τ = V/v0 = 2 мин, начальная концентрация CA0 = 30 моль/л. Реальные концентрации рассчитывали по данным программы: CA = CA0·(1−X), CR = CA0·Y, CS = CA0·Z; производительность по целевому продукту ΠR = v0·CR = 3·CR (кмоль/ч); интегральная селективность SR = Y/X.
+По степени превращения X и по производительности ΠR во всех трёх кинетических случаях эффективнее РИВ. При том же объёме и расходе в вытеснении средняя концентрация реагента A вдоль аппарата выше, чем выходная, поэтому скорость целевой стадии A → R больше. В РИС-н состав во всём объёме равен выходному: реакция идёт при уже низкой CA, скорость целевой стадии падает. При τ = 2 мин получено: случай 1 — X = 0,546 (РИВ) против 0,413 (РИС-н), ΠR = 30,46 против 20,66 кмоль/ч; случай 2 — X = 0,699 против 0,545, ΠR = 40,00 против 27,27 кмоль/ч; случай 3 — X = 0,699 против 0,545, ΠR = 50,84 против 36,95 кмоль/ч.
+По селективности РИВ также предпочтителен: SR = 0,620 против 0,556 (случай 1), 0,636 против 0,556 (случай 2), 0,808 против 0,753 (случай 3). В РИС-н интегральная селективность совпадает с дифференциальной на выходе, так как весь объём работает при выходном составе. В РИВ целевой продукт образуется при более высокой CA на начальном участке, доля побочного превращения R → S меньше.
+Среди кинетических вариантов наименее выгоден случай 1 (n1 = 2, n2 = 1): второй порядок по A замедляет целевую реакцию по мере расходования реагента, поэтому X и ΠR минимальны. Случаи 2 и 3 имеют одинаковый первый порядок стадии A → R, поэтому степени превращения в каждом типе реактора совпадают. Наилучший результат даёт случай 3 (n2 = 2): побочная реакция второго порядка по R замедлена при малых CR, селективность и выход целевого продукта максимальны (в РИВ CR = 16,95 моль/л, ΠR = 50,84 кмоль/ч).
+Итог: при заданных V и v0 процесс целесообразнее вести в реакторе идеального вытеснения; оптимальная кинетика из трёх рассмотренных — случай 3. График Ci(τ) построен для случая 1: CA монотонно снижается, CR выходит на пологий максимум к τ ≈ 1,8–2 мин, CS непрерывно растёт — типичная картина последовательной схемы A → R → S.</t>
         </is>
       </c>
     </row>
@@ -3828,10 +3828,16 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:G28"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G22"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reaktory_variant2/Реакторы_вариант2_графики.xlsx
+++ b/reaktory_variant2/Реакторы_вариант2_графики.xlsx
@@ -3582,7 +3582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3807,14 +3807,12 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="220" customHeight="1">
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>Моделирование последовательной реакции A → R → S выполнено в изотермическом режиме (T = 150 °C) для реакторов идеального смешения непрерывного действия (РИС-н) и идеального вытеснения (РИВ) одинакового объёма: V = 100 л, v0 = 50 л/мин, условное время пребывания τ = V/v0 = 2 мин, начальная концентрация CA0 = 30 моль/л. Реальные концентрации рассчитывали по данным программы: CA = CA0·(1−X), CR = CA0·Y, CS = CA0·Z; производительность по целевому продукту ΠR = v0·CR = 3·CR (кмоль/ч); интегральная селективность SR = Y/X.
-По степени превращения X и по производительности ΠR во всех трёх кинетических случаях эффективнее РИВ. При том же объёме и расходе в вытеснении средняя концентрация реагента A вдоль аппарата выше, чем выходная, поэтому скорость целевой стадии A → R больше. В РИС-н состав во всём объёме равен выходному: реакция идёт при уже низкой CA, скорость целевой стадии падает. При τ = 2 мин получено: случай 1 — X = 0,546 (РИВ) против 0,413 (РИС-н), ΠR = 30,46 против 20,66 кмоль/ч; случай 2 — X = 0,699 против 0,545, ΠR = 40,00 против 27,27 кмоль/ч; случай 3 — X = 0,699 против 0,545, ΠR = 50,84 против 36,95 кмоль/ч.
-По селективности РИВ также предпочтителен: SR = 0,620 против 0,556 (случай 1), 0,636 против 0,556 (случай 2), 0,808 против 0,753 (случай 3). В РИС-н интегральная селективность совпадает с дифференциальной на выходе, так как весь объём работает при выходном составе. В РИВ целевой продукт образуется при более высокой CA на начальном участке, доля побочного превращения R → S меньше.
-Среди кинетических вариантов наименее выгоден случай 1 (n1 = 2, n2 = 1): второй порядок по A замедляет целевую реакцию по мере расходования реагента, поэтому X и ΠR минимальны. Случаи 2 и 3 имеют одинаковый первый порядок стадии A → R, поэтому степени превращения в каждом типе реактора совпадают. Наилучший результат даёт случай 3 (n2 = 2): побочная реакция второго порядка по R замедлена при малых CR, селективность и выход целевого продукта максимальны (в РИВ CR = 16,95 моль/л, ΠR = 50,84 кмоль/ч).
-Итог: при заданных V и v0 процесс целесообразнее вести в реакторе идеального вытеснения; оптимальная кинетика из трёх рассмотренных — случай 3. График Ci(τ) построен для случая 1: CA монотонно снижается, CR выходит на пологий максимум к τ ≈ 1,8–2 мин, CS непрерывно растёт — типичная картина последовательной схемы A → R → S.</t>
+          <t>При одинаковых V, v0 и τ = 2 мин во всех трёх случаях РИВ лучше РИС-н: выше степень превращения X, селективность SR и производительность ΠR по целевому продукту R. В РИС-н весь объём работает при низкой выходной CA, поэтому стадия A → R идёт медленнее.
+Случай 1 (n1 = 2) наименее выгоден — целевая реакция тормозится по мере расхода A. Случаи 2 и 3 дают одинаковое X (n1 = 1), но случай 3 (n2 = 2) лучший: побочная R → S замедлена, в РИВ ΠR = 50,84 кмоль/ч против 30,46 и 40,00 в случаях 1 и 2.
+Вывод: процесс целесообразнее вести в РИВ; из трёх кинетик оптимален случай 3.</t>
         </is>
       </c>
     </row>
@@ -3824,19 +3822,9 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A12:G28"/>
+    <mergeCell ref="A12:G18"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/reaktory_variant2/Реакторы_вариант2_графики.xlsx
+++ b/reaktory_variant2/Реакторы_вариант2_графики.xlsx
@@ -295,12 +295,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Графики_случай1'!$A$6:$A$16</f>
+              <f>'Графики_случай1'!$A$6:$A$17</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Графики_случай1'!$C$6:$C$16</f>
+              <f>'Графики_случай1'!$C$6:$C$17</f>
             </numRef>
           </yVal>
           <smooth val="1"/>
@@ -337,12 +337,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Графики_случай1'!$A$6:$A$16</f>
+              <f>'Графики_случай1'!$A$6:$A$17</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Графики_случай1'!$E$6:$E$16</f>
+              <f>'Графики_случай1'!$E$6:$E$17</f>
             </numRef>
           </yVal>
           <smooth val="1"/>
@@ -377,12 +377,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Графики_случай1'!$A$6:$A$16</f>
+              <f>'Графики_случай1'!$A$6:$A$17</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Графики_случай1'!$G$6:$G$16</f>
+              <f>'Графики_случай1'!$G$6:$G$17</f>
             </numRef>
           </yVal>
           <smooth val="1"/>
@@ -533,12 +533,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Графики_случай1'!$A$22:$A$32</f>
+              <f>'Графики_случай1'!$A$23:$A$33</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Графики_случай1'!$C$22:$C$32</f>
+              <f>'Графики_случай1'!$C$23:$C$33</f>
             </numRef>
           </yVal>
           <smooth val="1"/>
@@ -575,12 +575,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Графики_случай1'!$A$22:$A$32</f>
+              <f>'Графики_случай1'!$A$23:$A$33</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Графики_случай1'!$E$22:$E$32</f>
+              <f>'Графики_случай1'!$E$23:$E$33</f>
             </numRef>
           </yVal>
           <smooth val="1"/>
@@ -615,12 +615,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Графики_случай1'!$A$22:$A$32</f>
+              <f>'Графики_случай1'!$A$23:$A$33</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Графики_случай1'!$G$22:$G$32</f>
+              <f>'Графики_случай1'!$G$23:$G$33</f>
             </numRef>
           </yVal>
           <smooth val="1"/>
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1467,462 +1467,494 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>14.217</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5.604</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.6449344231134765</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>30.537</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B17" s="8" t="n">
         <v>0.5455</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C17" s="7" t="n">
         <v>13.635</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D17" s="8" t="n">
         <v>0.3384</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E17" s="7" t="n">
         <v>10.152</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="8" t="n">
         <v>0.2071</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G17" s="7" t="n">
         <v>6.213</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H17" s="8" t="n">
         <v>0.6203</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I17" s="8" t="n">
         <v>0.6203483043079743</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J17" s="7" t="n">
         <v>30.456</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>РИС-н, случай 1: n1=2, n2=1; k1=0,6 л/(моль·мин); k2=0,4 мин⁻¹ (профиль по τ)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>S (дифф.)</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>SR = Y/X</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>ΠR, кмоль/ч</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="5" t="n">
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>0.09769789141815066</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>27.06906325745548</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>0.09046101057236126</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>2.713830317170838</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>0.007236880845788902</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>0.2171064253736671</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>0.9259259259259213</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>0.9259259259259213</v>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>8.141490951512514</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="B24" s="8" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>27.069</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>0.9263050153531218</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>8.145</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>0.1666666666666669</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>24.99999999999999</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>0.1436781609195402</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>4.310344827586205</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0.02298850574712643</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.6896551724137929</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0.86206896551724</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0.86206896551724</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>12.93103448275862</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="B25" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>24.999</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>4.311</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.8620275944811038</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>12.933</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>0.2193750900259294</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>23.41874729922212</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>0.176915395182201</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>5.307461855466031</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>0.04245969484372825</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>1.273790845311848</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>0.8064516129032255</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>0.8064516129032255</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>15.92238556639809</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="B26" s="8" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>23.418</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>5.307</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>0.8065</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>0.8062898814949863</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>15.921</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>0.261665886392181</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>22.15002340823457</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>0.1982317321152886</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>5.946951963458658</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>0.06343415427689236</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>1.903024628306771</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0.7575757575757573</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0.7575757575757573</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>17.84085589037597</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="B27" s="6" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>22.149</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>5.946</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1.902</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.757355750859763</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>17.838</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>0.2967425904511853</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>21.09772228646444</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>0.2119589931794183</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>6.358769795382548</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>0.08478359727176732</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>2.543507918153019</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>0.7142857142857149</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>0.7142857142857149</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>19.07630938614765</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="B28" s="8" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>21.099</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>6.359999999999999</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>0.7145264577013818</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>19.08</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>0.3265475275283187</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>20.20357417415044</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>0.2206402213029181</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>6.619206639087543</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>0.1059073062254007</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>3.177219186762021</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0.6756756756756758</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>0.6756756756756758</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>19.85761991726263</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="B29" s="6" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>20.205</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.2206</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>6.617999999999999</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>0.6757</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.6756508422664624</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>19.854</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
         <v>1.4</v>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>0.3523444632249347</v>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>19.42966610325196</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>0.2258618354005988</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>6.775855062017964</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>0.1264826278243353</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>3.79447883473006</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>0.64102564102564</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>0.64102564102564</v>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>20.32756518605389</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="B30" s="8" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>19.431</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0.2259</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>6.776999999999999</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>0.6412148736871984</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>20.331</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>0.3749999999999999</v>
-      </c>
-      <c r="C30" s="5" t="n">
+      <c r="B31" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="C31" s="5" t="n">
         <v>18.75</v>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>0.2286585365853659</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>6.859756097560979</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>0.1463414634146342</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>4.390243902439027</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>0.609756097560976</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>0.609756097560976</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>20.57926829268294</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="D31" s="6" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>6.861</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.6098666666666667</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>20.583</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
         <v>1.8</v>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>0.3951330930860374</v>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>18.14600720741888</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>0.2297285424918822</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>6.891856274756465</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>0.1654045505941552</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>4.962136517824655</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>0.5813953488372092</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>0.5813953488372092</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>20.6755688242694</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="B32" s="8" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>18.147</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>0.2297</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>6.891</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>4.962</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>0.5813718046064287</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>20.673</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B33" s="6" t="n">
         <v>0.4132</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C33" s="5" t="n">
         <v>17.604</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D33" s="6" t="n">
         <v>0.2296</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E33" s="5" t="n">
         <v>6.888</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F33" s="6" t="n">
         <v>0.1836</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G33" s="5" t="n">
         <v>5.508</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H33" s="6" t="n">
         <v>0.5556</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>0.5556631171345595</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J33" s="5" t="n">
         <v>20.664</v>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Примечание: X, Y, Z — с экрана программы (безразмерные, C0=1). CA = 30·(1−X), CR = 30·Y, CS = 30·Z, моль/л. ΠR = v0·CR = 3·CR, кмоль/ч. Для РИС-н на графике — расчёт при тех же τ, на τ=2 подставлены значения с экрана (X=0,4132; Y=0,2296; Z=0,1836).</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37"/>
+    <row r="38"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A35:J37"/>
+    <mergeCell ref="A36:J38"/>
+    <mergeCell ref="A21:J21"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A20:J20"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1937,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2340,1236 +2372,2132 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>14.217</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.179</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1868</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>5.604</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6449344231134765</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>30.537</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B16" s="8" t="n">
         <v>0.5455</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="7" t="n">
         <v>13.635</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D16" s="8" t="n">
         <v>0.3384</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E16" s="7" t="n">
         <v>10.152</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F16" s="8" t="n">
         <v>0.2071</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G16" s="7" t="n">
         <v>6.213</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H16" s="8" t="n">
         <v>0.6203</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I16" s="8" t="n">
         <v>0.6203483043079743</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J16" s="7" t="n">
         <v>30.456</v>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>РИС-н (экран программы), случай 1: n1=2, n2=1; k1=0,6 л/(моль·мин); k2=0,4 мин⁻¹</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>РИС-н, случай 1: n1=2, n2=1; k1=0,6 л/(моль·мин); k2=0,4 мин⁻¹</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>S (дифф.)</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>SR = Y/X</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>ΠR, кмоль/ч</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="5" t="n">
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>27.069</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0.9263050153531218</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>8.145</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>24.999</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.311</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.8620275944811038</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>12.933</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>23.418</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>5.307</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0.8065</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>0.8062898814949863</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>15.921</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>22.149</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>5.946</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.0634</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1.902</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0.757355750859763</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>17.838</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>21.099</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>6.359999999999999</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0.7145264577013818</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>19.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>20.205</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.2206</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>6.617999999999999</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.6757</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.6756508422664624</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>19.854</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>19.431</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>0.2259</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>6.776999999999999</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0.6412148736871984</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>20.331</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>6.861</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.6098666666666667</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>20.583</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>18.147</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>0.2297</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>6.891</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>4.962</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>0.5813718046064287</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>20.673</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B32" s="6" t="n">
         <v>0.4132</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C32" s="5" t="n">
         <v>17.604</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D32" s="6" t="n">
         <v>0.2296</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E32" s="5" t="n">
         <v>6.888</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F32" s="6" t="n">
         <v>0.1836</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G32" s="5" t="n">
         <v>5.508</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H32" s="6" t="n">
         <v>0.5556</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I32" s="6" t="n">
         <v>0.5556631171345595</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J32" s="5" t="n">
         <v>20.664</v>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>РИВ, случай 2: n1=n2=1; k1=0,6 мин⁻¹; k2=0,4 мин⁻¹</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>S (дифф.)</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>SR = Y/X</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>ΠR, кмоль/ч</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B30" s="8" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>0.1086</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>3.258</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>0.9603</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>0.9602122015915119</v>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>9.774000000000001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>0.2134</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>23.598</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>0.1965</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>5.895</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>0.9211</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>0.9208059981255857</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>17.685</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B32" s="8" t="n">
-        <v>0.3023</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>20.931</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>0.2669</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>8.007000000000001</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>0.8827</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>0.8828977836586173</v>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>24.021</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>0.3812</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>18.564</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>0.3221</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>9.663</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0.0591</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>1.773</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0.8449</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0.8449632738719832</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>28.989</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="8" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>16.464</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>10.935</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>0.8079</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>0.807845744680851</v>
-      </c>
-      <c r="J34" s="7" t="n">
-        <v>32.805</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>14.604</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>0.3961</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>0.1172</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>3.516</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>0.7717000000000001</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>0.7718238503507405</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>35.649</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="B36" s="8" t="n">
-        <v>0.5683</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>12.951</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>0.4185</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>12.555</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>0.1498</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>4.494</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>0.7364000000000001</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>0.7364068273799049</v>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>37.665</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>11.487</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>0.4332</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>12.996</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>0.1839</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>5.517</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>0.7019931939718036</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>38.988</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="B38" s="8" t="n">
-        <v>0.6604</v>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>10.188</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>0.4415</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>13.245</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>0.2189</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>6.567</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>0.6685</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>0.668534221683828</v>
-      </c>
-      <c r="J38" s="7" t="n">
-        <v>39.735</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.6988</v>
+        <v>0</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>9.036000000000001</v>
+        <v>30</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.4444</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>13.332</v>
+        <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.2544</v>
+        <v>0</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>7.632000000000001</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.6359</v>
+        <v>1</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.6359473382942187</v>
+        <v>1</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>39.996</v>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>РИС-н (экран программы), случай 2: n1=n2=1; k1=0,6 мин⁻¹; k2=0,4 мин⁻¹</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>τ, мин</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>CA, моль/л</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>CR, моль/л</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>CS, моль/л</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>S (дифф.)</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>SR = Y/X</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>ΠR, кмоль/ч</t>
-        </is>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>26.607</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>3.258</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>0.9603</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>0.9602122015915119</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>9.774000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>23.598</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>0.9211</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>0.9208059981255857</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>17.685</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>20.931</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>8.007000000000001</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>0.8827</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>0.8828977836586173</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>24.021</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>18.564</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>9.663</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1.773</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>0.8449</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>0.8449632738719832</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>28.989</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>0.807845744680851</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>32.805</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>0</v>
+        <v>0.5132</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>30</v>
+        <v>14.604</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0</v>
+        <v>0.3961</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>11.883</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0</v>
+        <v>3.516</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>1</v>
+        <v>0.7718238503507405</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0</v>
+        <v>35.649</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>12.951</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>12.555</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>4.494</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>0.7364068273799049</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>37.665</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>0.6171</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>11.487</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>12.996</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>5.517</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>0.7019931939718036</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>38.988</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>10.188</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>13.245</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>6.567</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>0.6685</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>0.668534221683828</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>39.735</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="8" t="n">
-        <v>0.5454</v>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>13.638</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>0.2424</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>7.272</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="J46" s="7" t="n">
-        <v>27.27</v>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>РИВ, случай 3: n1=1, n2=2; k1=0,6 мин⁻¹; k2=0,4 л/(моль·мин)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="B49" s="6" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>9.036000000000001</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>7.632000000000001</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>0.6359</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>0.6359473382942187</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>39.996</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>РИС-н, случай 2: n1=n2=1; k1=0,6 мин⁻¹; k2=0,4 мин⁻¹</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>S (дифф.)</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>SR = Y/X</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>ΠR, кмоль/ч</t>
         </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>26.607</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>0.1127</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>3.381</v>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H54" s="8" t="n">
-        <v>0.9969</v>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>0.9964633068081343</v>
-      </c>
-      <c r="J54" s="7" t="n">
-        <v>10.143</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>0.2134</v>
+        <v>0</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>23.598</v>
+        <v>30</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.2108</v>
+        <v>0</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>6.324</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.0025</v>
+        <v>0</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.9881</v>
+        <v>1</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.9878163074039362</v>
+        <v>1</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>18.972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="B56" s="8" t="n">
-        <v>0.3023</v>
+        <v>0.1071</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>20.931</v>
+        <v>26.787</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0.2946</v>
+        <v>0.0992</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>8.837999999999999</v>
+        <v>2.976</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.0077</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>0.231</v>
+        <v>0.237</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.9744</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.9745286139596426</v>
+        <v>0.9262371615312791</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>26.514</v>
+        <v>8.927999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>0.3812</v>
+        <v>0.1935</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>18.564</v>
+        <v>24.195</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>0.3647</v>
+        <v>0.1669</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>10.941</v>
+        <v>5.007</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.0165</v>
+        <v>0.0267</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.495</v>
+        <v>0.801</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0.9566</v>
+        <v>0.8621</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.9567156348373558</v>
+        <v>0.8625322997416021</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>32.823</v>
+        <v>15.021</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="B58" s="8" t="n">
-        <v>0.4512</v>
+        <v>0.2647</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>16.464</v>
+        <v>22.059</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>0.4222</v>
+        <v>0.2135</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>12.666</v>
+        <v>6.405</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0.029</v>
+        <v>0.0512</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>0.87</v>
+        <v>1.536</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.9357</v>
+        <v>0.8065</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.93572695035461</v>
+        <v>0.8065734794106536</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>37.998</v>
+        <v>19.215</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>0.5132</v>
+        <v>0.3243</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>14.604</v>
+        <v>20.271</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.4683</v>
+        <v>0.2457</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>14.049</v>
+        <v>7.371</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.0449</v>
+        <v>0.0786</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.347</v>
+        <v>2.358</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>0.9124</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.9125097427903351</v>
+        <v>0.757631822386679</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>42.147</v>
+        <v>22.113</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="B60" s="8" t="n">
-        <v>0.5683</v>
+        <v>0.375</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>12.951</v>
+        <v>18.75</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>0.5044</v>
+        <v>0.2679</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>15.132</v>
+        <v>8.037000000000001</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>0.0639</v>
+        <v>0.1071</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>1.917</v>
+        <v>3.213</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>0.8875</v>
+        <v>0.7143</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.8875593876473692</v>
+        <v>0.7144</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>45.39599999999999</v>
+        <v>24.111</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="B61" s="6" t="n">
-        <v>0.6171</v>
+        <v>0.4186</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>11.487</v>
+        <v>17.442</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>0.5317</v>
+        <v>0.2828</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>15.951</v>
+        <v>8.484</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1358</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>2.565</v>
+        <v>4.074</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>0.8615</v>
+        <v>0.6757</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.8616107600064818</v>
+        <v>0.6755852842809364</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>47.85299999999999</v>
+        <v>25.452</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="B62" s="8" t="n">
-        <v>0.6604</v>
+        <v>0.4565</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>10.188</v>
+        <v>16.305</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>0.5514</v>
+        <v>0.2926</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>16.542</v>
+        <v>8.778</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>0.109</v>
+        <v>0.1639</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>3.27</v>
+        <v>4.917</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>0.835</v>
+        <v>0.641</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0.8349485160508783</v>
+        <v>0.6409638554216868</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>49.626</v>
+        <v>26.334</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>15.306</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>8.961</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>0.6098407513270723</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>26.883</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>14.424</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>9.057</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>6.522</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>0.5814</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>0.5814714946070878</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>27.171</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B65" s="6" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>13.638</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>0.2424</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>7.272</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>27.27</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>РИВ, случай 3: n1=1, n2=2; k1=0,6 мин⁻¹; k2=0,4 л/(моль·мин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>τ, мин</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>CA, моль/л</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>CR, моль/л</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>CS, моль/л</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>S (дифф.)</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>SR = Y/X</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>ΠR, кмоль/ч</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>26.607</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>3.381</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>0.9964633068081343</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>10.143</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>23.598</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>0.2108</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>6.324</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>0.9881</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>0.9878163074039362</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>18.972</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>20.931</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>8.837999999999999</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>0.9744</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>0.9745286139596426</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>26.514</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>18.564</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>10.941</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>0.9566</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>0.9567156348373558</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>32.823</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>16.464</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>12.666</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>0.9357</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>0.93572695035461</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>37.998</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>14.604</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>14.049</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1.347</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>0.9124</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>0.9125097427903351</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>42.147</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>12.951</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>15.132</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>1.917</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>0.8875593876473692</v>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>45.39599999999999</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>0.6171</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>11.487</v>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>0.5317</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>15.951</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>0.8615</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>0.8616107600064818</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>47.85299999999999</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>10.188</v>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>16.542</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="I81" s="8" t="n">
+        <v>0.8349485160508783</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>49.626</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B82" s="6" t="n">
         <v>0.6988</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>9.036000000000001</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D82" s="6" t="n">
         <v>0.5649</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E82" s="5" t="n">
         <v>16.947</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F82" s="6" t="n">
         <v>0.1339</v>
       </c>
-      <c r="G63" s="5" t="n">
+      <c r="G82" s="5" t="n">
         <v>4.016999999999999</v>
       </c>
-      <c r="H63" s="6" t="n">
+      <c r="H82" s="6" t="n">
         <v>0.8083</v>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I82" s="6" t="n">
         <v>0.8083858042358328</v>
       </c>
-      <c r="J63" s="5" t="n">
+      <c r="J82" s="5" t="n">
         <v>50.84099999999999</v>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>РИС-н (экран программы), случай 3: n1=1, n2=2; k1=0,6 мин⁻¹; k2=0,4 л/(моль·мин)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>РИС-н, случай 3: n1=1, n2=2; k1=0,6 мин⁻¹; k2=0,4 л/(моль·мин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>τ, мин</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>CA, моль/л</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>CR, моль/л</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>CS, моль/л</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>S (дифф.)</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>SR = Y/X</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>ΠR, кмоль/ч</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="B69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="5" t="n">
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="6" t="n">
+      <c r="D88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I69" s="6" t="n">
+      <c r="I88" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="n">
+      <c r="J88" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>26.787</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>3.186</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>0.9915966386554622</v>
+      </c>
+      <c r="J89" s="7" t="n">
+        <v>9.558</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>24.195</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>5.637</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>0.9710594315245479</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>16.911</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>22.059</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>7.491000000000001</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="I91" s="8" t="n">
+        <v>0.94333207404609</v>
+      </c>
+      <c r="J91" s="7" t="n">
+        <v>22.473</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>20.271</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>8.886000000000001</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>0.9134</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>0.9133518347209375</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>26.658</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>9.933</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="I93" s="8" t="n">
+        <v>0.8829333333333333</v>
+      </c>
+      <c r="J93" s="7" t="n">
+        <v>29.799</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>17.442</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>10.719</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>0.8536</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>0.8535594839942665</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>32.157</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>16.305</v>
+      </c>
+      <c r="D95" s="8" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>0.8257</v>
+      </c>
+      <c r="I95" s="8" t="n">
+        <v>0.8258488499452354</v>
+      </c>
+      <c r="J95" s="7" t="n">
+        <v>33.93</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>15.306</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>11.748</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>2.946</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>0.7996</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>0.7995100040832993</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>35.244</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>14.424</v>
+      </c>
+      <c r="D97" s="8" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>12.078</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>3.501</v>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>0.7753</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>0.7754237288135594</v>
+      </c>
+      <c r="J97" s="7" t="n">
+        <v>36.234</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B70" s="8" t="n">
+      <c r="B98" s="6" t="n">
         <v>0.5454</v>
       </c>
-      <c r="C70" s="7" t="n">
+      <c r="C98" s="5" t="n">
         <v>13.638</v>
       </c>
-      <c r="D70" s="8" t="n">
+      <c r="D98" s="6" t="n">
         <v>0.4106</v>
       </c>
-      <c r="E70" s="7" t="n">
+      <c r="E98" s="5" t="n">
         <v>12.318</v>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F98" s="6" t="n">
         <v>0.1349</v>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G98" s="5" t="n">
         <v>4.047</v>
       </c>
-      <c r="H70" s="8" t="n">
+      <c r="H98" s="6" t="n">
         <v>0.7528</v>
       </c>
-      <c r="I70" s="8" t="n">
+      <c r="I98" s="6" t="n">
         <v>0.7528419508617529</v>
       </c>
-      <c r="J70" s="7" t="n">
+      <c r="J98" s="5" t="n">
         <v>36.954</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A70:J70"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A86:J86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
